--- a/data_kpi.xlsx
+++ b/data_kpi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neosmacbook/Desktop/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8C4C826-E341-7A43-9498-24DA73A30E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92A9AA80-7E42-6548-A05A-7BA8DC145219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" tabRatio="588" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" tabRatio="588" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="單位 (分隊)" sheetId="23" r:id="rId1"/>

--- a/data_kpi.xlsx
+++ b/data_kpi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neosmacbook/Desktop/Dashboard/戰情室報表更新/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37D039CD-DD4E-6E41-A1BB-1ADD85BC17B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F39B7778-BFA6-4E42-92F0-CC8D5924EC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" tabRatio="588" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId6"/>
+    <pivotCache cacheId="4" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -29485,7 +29485,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000000000000}" name="樞紐分析表1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="數值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000000000000}" name="樞紐分析表1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="數值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField axis="axisRow" showAll="0">

--- a/data_kpi.xlsx
+++ b/data_kpi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neosmacbook/Desktop/Dashboard/戰情室報表更新/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0418442B-24EE-6441-9C7E-40758F7B2E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B017722-D5BD-7546-BA6D-CB8CC28EF138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" tabRatio="588" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId6"/>
+    <pivotCache cacheId="6" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -29487,7 +29487,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000000000000}" name="樞紐分析表1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="數值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000000000000}" name="樞紐分析表1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="數值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField axis="axisRow" showAll="0">

--- a/data_kpi.xlsx
+++ b/data_kpi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neosmacbook/Desktop/Dashboard/戰情室報表更新/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B017722-D5BD-7546-BA6D-CB8CC28EF138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{002708CD-C55F-E84B-A880-E5412221291B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" tabRatio="588" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
